--- a/tams-common-basicdata/src/main/resources/tpl/marketdata/exchangerateinfo/ComExchangeRateInfo001.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/marketdata/exchangerateinfo/ComExchangeRateInfo001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpace3.0\tams-common-basicdata\src\main\resources\tpl\marketdata\exchangerateinfo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20385" windowHeight="8370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20390" windowHeight="8370"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,23 +19,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>货币对</t>
   </si>
   <si>
-    <t>外汇类型</t>
-  </si>
-  <si>
     <t>交易日期</t>
   </si>
   <si>
     <t>期限</t>
   </si>
   <si>
-    <t>到期日</t>
-  </si>
-  <si>
     <t>数据来源</t>
   </si>
   <si>
@@ -44,6 +43,10 @@
   </si>
   <si>
     <t>最低价(元)</t>
+  </si>
+  <si>
+    <t>中间价(元)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -108,77 +111,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -189,7 +127,7 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="373737"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -442,18 +380,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="13.375" customWidth="1"/>
-    <col min="4" max="4" width="7.875" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
-    <col min="7" max="7" width="10.25" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" customWidth="1"/>
+    <col min="3" max="3" width="7.90625" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" customWidth="1"/>
+    <col min="5" max="6" width="10.26953125" customWidth="1"/>
+    <col min="7" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,25 +401,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
